--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72D9E90-D5B4-4B9C-9E2A-7D696642A2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BCC1DF-84BC-4FBF-930A-2D6D41A89313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>codigo</t>
   </si>
@@ -40,18 +40,6 @@
   </si>
   <si>
     <t>dolar</t>
-  </si>
-  <si>
-    <t>AR16217038</t>
-  </si>
-  <si>
-    <t>AR6781703G</t>
-  </si>
-  <si>
-    <t>AR7971602HD</t>
-  </si>
-  <si>
-    <t>AR9191602HD</t>
   </si>
 </sst>
 </file>
@@ -485,121 +473,62 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>3147</v>
-      </c>
+      <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="3">
-        <v>415000</v>
-      </c>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>104058</v>
-      </c>
+      <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="3">
-        <v>587000</v>
-      </c>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>3148</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="3">
-        <v>455000</v>
-      </c>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>4214</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="3">
-        <v>446000</v>
-      </c>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>103269</v>
-      </c>
+      <c r="A8" s="3"/>
       <c r="B8" s="3"/>
-      <c r="C8" s="3">
-        <v>445000</v>
-      </c>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7500584</v>
-      </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="3">
-        <v>415000</v>
-      </c>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>7500589</v>
-      </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="3">
-        <v>455000</v>
-      </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>7500148</v>
-      </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="3">
-        <v>455000</v>
-      </c>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>7500150</v>
-      </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="3">
-        <v>500000</v>
-      </c>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="3">
-        <v>415000</v>
-      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="3">
-        <v>455000</v>
-      </c>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="3">
-        <v>415000</v>
-      </c>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="3">
-        <v>455000</v>
-      </c>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BCC1DF-84BC-4FBF-930A-2D6D41A89313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742D17AE-34AB-4E5C-B3C5-D917253EF7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -458,7 +458,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1535</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742D17AE-34AB-4E5C-B3C5-D917253EF7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844F6132-245D-4963-B0F0-1CFC844BFAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -458,7 +458,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1545</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844F6132-245D-4963-B0F0-1CFC844BFAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A606D662-DA77-4BFA-8E97-6FD991D67176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A606D662-DA77-4BFA-8E97-6FD991D67176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A0C6CD-56C2-4EE7-AC4F-4DAF7D26240F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -458,7 +458,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1535</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/public/ofertas.xlsx
+++ b/public/ofertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A0C6CD-56C2-4EE7-AC4F-4DAF7D26240F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9647A60B-B8F3-4D36-B3C2-F8923C180DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16801F8F-C285-42AA-9A09-3B0ED6F11ADA}"/>
   </bookViews>
@@ -458,7 +458,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1550</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
